--- a/data/trans_orig/P59A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P59A-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si viven actualmente en pareja en 2007</t>
+          <t>Población según si viven actualmente en pareja en 2007 (tasa de respuesta: 98,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21861</t>
+          <t>21448</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41920</t>
+          <t>42861</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13610</t>
+          <t>13539</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30759</t>
+          <t>31081</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40561</t>
+          <t>39649</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67811</t>
+          <t>65914</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,47%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>103391</t>
+          <t>102450</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>123450</t>
+          <t>123863</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93341</t>
+          <t>93019</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>110490</t>
+          <t>110561</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>201600</t>
+          <t>203497</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>228850</t>
+          <t>229762</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>85,28%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12480</t>
+          <t>12573</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28702</t>
+          <t>27495</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28554</t>
+          <t>27654</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49754</t>
+          <t>51261</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45520</t>
+          <t>44695</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72246</t>
+          <t>72413</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94032</t>
+          <t>95239</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>110254</t>
+          <t>110161</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>114614</t>
+          <t>113107</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>135814</t>
+          <t>136714</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>214856</t>
+          <t>214689</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>241582</t>
+          <t>242407</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,43%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24126</t>
+          <t>23732</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46069</t>
+          <t>44916</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>928</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8876</t>
+          <t>8040</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26817</t>
+          <t>26296</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51449</t>
+          <t>48930</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113101</t>
+          <t>114254</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>135044</t>
+          <t>135438</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36428</t>
+          <t>37264</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44364</t>
+          <t>44376</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>153025</t>
+          <t>155544</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>177657</t>
+          <t>178178</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>87,14%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51655</t>
+          <t>51689</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81656</t>
+          <t>82478</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25161</t>
+          <t>26565</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48749</t>
+          <t>49560</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84290</t>
+          <t>84272</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123384</t>
+          <t>124965</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>328180</t>
+          <t>327358</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>358181</t>
+          <t>358147</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>260338</t>
+          <t>259527</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>283926</t>
+          <t>282522</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>595539</t>
+          <t>593958</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>634633</t>
+          <t>634651</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15747</t>
+          <t>15034</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34115</t>
+          <t>34287</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17513</t>
+          <t>17432</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36272</t>
+          <t>37639</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35787</t>
+          <t>37776</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64612</t>
+          <t>64986</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>127395</t>
+          <t>127223</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>145763</t>
+          <t>146476</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>160685</t>
+          <t>159318</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>179444</t>
+          <t>179525</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>293855</t>
+          <t>293481</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>322680</t>
+          <t>320691</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,46%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4257</t>
+          <t>4861</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>9655</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25778</t>
+          <t>26466</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10036</t>
+          <t>10353</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28099</t>
+          <t>27173</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>282919</t>
+          <t>282315</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>515596</t>
+          <t>514908</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>532718</t>
+          <t>531719</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>800451</t>
+          <t>801377</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>818514</t>
+          <t>818197</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>149905</t>
+          <t>148176</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>200056</t>
+          <t>199818</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>117584</t>
+          <t>119396</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>164306</t>
+          <t>164758</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>281515</t>
+          <t>280883</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>351900</t>
+          <t>352983</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1085681</t>
+          <t>1085919</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1135832</t>
+          <t>1137561</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1216884</t>
+          <t>1216432</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1263606</t>
+          <t>1261794</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2315027</t>
+          <t>2313944</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2385412</t>
+          <t>2386044</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,47%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si viven actualmente en pareja en 2012</t>
+          <t>Población según si viven actualmente en pareja en 2012 (tasa de respuesta: 97,56%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24492</t>
+          <t>24420</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47286</t>
+          <t>47345</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17951</t>
+          <t>18778</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37916</t>
+          <t>39296</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48952</t>
+          <t>49728</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79468</t>
+          <t>78999</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,45%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>105449</t>
+          <t>105390</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>128243</t>
+          <t>128315</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>77596</t>
+          <t>76216</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>97561</t>
+          <t>96734</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>188779</t>
+          <t>189248</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>219295</t>
+          <t>218519</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,46%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13123</t>
+          <t>13564</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33059</t>
+          <t>32602</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17668</t>
+          <t>17759</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37441</t>
+          <t>35894</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33535</t>
+          <t>34478</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61772</t>
+          <t>61539</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>101171</t>
+          <t>101628</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>121107</t>
+          <t>120666</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>80220</t>
+          <t>81767</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>99993</t>
+          <t>99902</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>190119</t>
+          <t>190352</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>218356</t>
+          <t>217413</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,31%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32586</t>
+          <t>33336</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57759</t>
+          <t>57741</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12229</t>
+          <t>11718</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27455</t>
+          <t>27330</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49112</t>
+          <t>48392</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78431</t>
+          <t>77335</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>136357</t>
+          <t>136375</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>161530</t>
+          <t>160780</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71041</t>
+          <t>71166</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86267</t>
+          <t>86778</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>214181</t>
+          <t>215277</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>243500</t>
+          <t>244220</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,46%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62070</t>
+          <t>61116</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96291</t>
+          <t>95024</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57508</t>
+          <t>57803</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>87129</t>
+          <t>87379</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>125952</t>
+          <t>128721</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>172395</t>
+          <t>175893</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,77%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>320812</t>
+          <t>322079</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>355033</t>
+          <t>355987</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>235643</t>
+          <t>235393</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>265264</t>
+          <t>264969</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>567481</t>
+          <t>563983</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>613924</t>
+          <t>611155</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>82,6%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24458</t>
+          <t>23546</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45699</t>
+          <t>45784</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27719</t>
+          <t>27816</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53281</t>
+          <t>52154</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>56567</t>
+          <t>56569</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90379</t>
+          <t>90813</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,96%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>177630</t>
+          <t>177545</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>198871</t>
+          <t>199783</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>229173</t>
+          <t>230300</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>254735</t>
+          <t>254638</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>415403</t>
+          <t>414969</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>449215</t>
+          <t>449213</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11996</t>
+          <t>12285</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30300</t>
+          <t>29886</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11966</t>
+          <t>12070</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29684</t>
+          <t>30725</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>255033</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>256959</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>455617</t>
+          <t>456031</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>473921</t>
+          <t>473632</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>713192</t>
+          <t>712151</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>730910</t>
+          <t>730806</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>186741</t>
+          <t>185926</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>242547</t>
+          <t>243598</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>178142</t>
+          <t>174627</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>231558</t>
+          <t>231653</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,47 +5476,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t>16,28%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>414321</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>376100</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>455811</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>14,79%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>13,43%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>16,27%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>414321</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>376419</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>456231</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>14,79%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>13,44%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1135924</t>
+          <t>1134873</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1191730</t>
+          <t>1192545</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1191255</t>
+          <t>1191160</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1244671</t>
+          <t>1248186</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,47 +5589,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
+          <t>83,72%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>87,73%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>2256</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>2386963</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>2345473</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>2425184</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>85,21%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>83,73%</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>87,48%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>2256</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>2386963</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>2345053</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>2424865</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>85,21%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>83,71%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,57%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si viven actualmente en pareja en 2016</t>
+          <t>Población según si viven actualmente en pareja en 2016 (tasa de respuesta: 97,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17338</t>
+          <t>16988</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37389</t>
+          <t>37326</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17981</t>
+          <t>17861</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38445</t>
+          <t>37679</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39514</t>
+          <t>39640</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67851</t>
+          <t>68038</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,91%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>149585</t>
+          <t>149648</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>169636</t>
+          <t>169986</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>116241</t>
+          <t>117007</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136705</t>
+          <t>136825</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>273809</t>
+          <t>273622</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>302146</t>
+          <t>302020</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,4%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33435</t>
+          <t>34651</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56572</t>
+          <t>57257</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18889</t>
+          <t>19048</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38575</t>
+          <t>39159</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57662</t>
+          <t>57243</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>87759</t>
+          <t>86143</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,58%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72135</t>
+          <t>71450</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>95272</t>
+          <t>94056</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>114458</t>
+          <t>113874</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>134144</t>
+          <t>133985</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>193981</t>
+          <t>195597</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>224078</t>
+          <t>224497</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,68%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20816</t>
+          <t>20683</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42187</t>
+          <t>41578</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20228</t>
+          <t>19908</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30696</t>
+          <t>31202</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55504</t>
+          <t>55500</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113442</t>
+          <t>114051</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>134813</t>
+          <t>134946</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48033</t>
+          <t>48353</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62059</t>
+          <t>61723</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>168386</t>
+          <t>168390</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>193194</t>
+          <t>192688</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,06%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79782</t>
+          <t>78737</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>113112</t>
+          <t>112629</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67857</t>
+          <t>67581</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102341</t>
+          <t>100110</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>155141</t>
+          <t>155197</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>202238</t>
+          <t>202344</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>299689</t>
+          <t>300172</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>333019</t>
+          <t>334064</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>313714</t>
+          <t>315945</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>348198</t>
+          <t>348474</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>626618</t>
+          <t>626512</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>673715</t>
+          <t>673659</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38835</t>
+          <t>39016</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>67883</t>
+          <t>66437</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37106</t>
+          <t>38145</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62757</t>
+          <t>64785</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82709</t>
+          <t>83741</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>120880</t>
+          <t>121954</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>226813</t>
+          <t>228259</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>255861</t>
+          <t>255680</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>253825</t>
+          <t>251797</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>279476</t>
+          <t>278437</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>490398</t>
+          <t>489324</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>528569</t>
+          <t>527537</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,3%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14165</t>
+          <t>13876</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17870</t>
+          <t>17649</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37120</t>
+          <t>38091</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23970</t>
+          <t>23302</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46229</t>
+          <t>45867</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>263321</t>
+          <t>263610</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>274295</t>
+          <t>274581</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>441985</t>
+          <t>441014</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>461235</t>
+          <t>461456</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>710363</t>
+          <t>710725</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>732622</t>
+          <t>733290</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>227607</t>
+          <t>225352</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>285309</t>
+          <t>287259</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>198142</t>
+          <t>197549</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>254976</t>
+          <t>254781</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>443195</t>
+          <t>439060</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>529112</t>
+          <t>519329</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1170984</t>
+          <t>1169034</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1228686</t>
+          <t>1230941</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1332746</t>
+          <t>1332941</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1389580</t>
+          <t>1390173</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2514903</t>
+          <t>2524686</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2600820</t>
+          <t>2604955</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,58%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si viven actualmente en pareja en 2023</t>
+          <t>Población según si viven actualmente en pareja en 2023 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33083</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60055</t>
+          <t>59521</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34062</t>
+          <t>34535</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55680</t>
+          <t>55638</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75170</t>
+          <t>74753</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106855</t>
+          <t>106715</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,71%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>141186</t>
+          <t>141720</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>168158</t>
+          <t>167170</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>158188</t>
+          <t>158230</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>179806</t>
+          <t>179333</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>308254</t>
+          <t>308394</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>339939</t>
+          <t>340356</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,99%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17903</t>
+          <t>17201</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41132</t>
+          <t>41549</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29003</t>
+          <t>29195</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49668</t>
+          <t>49992</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51754</t>
+          <t>51254</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82335</t>
+          <t>80280</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>153602</t>
+          <t>153185</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>176831</t>
+          <t>177533</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>130855</t>
+          <t>130531</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>151520</t>
+          <t>151328</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>292923</t>
+          <t>294978</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>323504</t>
+          <t>324004</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,34%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31156</t>
+          <t>31166</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59236</t>
+          <t>58317</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4878</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15070</t>
+          <t>14924</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38351</t>
+          <t>38292</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67748</t>
+          <t>68465</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,44%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>122894</t>
+          <t>123813</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>150974</t>
+          <t>150964</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61748</t>
+          <t>61894</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71940</t>
+          <t>71876</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>191200</t>
+          <t>190483</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>220597</t>
+          <t>220656</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,21%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76127</t>
+          <t>76236</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>120369</t>
+          <t>121044</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53088</t>
+          <t>53829</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81538</t>
+          <t>82232</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>138294</t>
+          <t>138588</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>190511</t>
+          <t>193727</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>379343</t>
+          <t>378668</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>423585</t>
+          <t>423476</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>298368</t>
+          <t>297674</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>326818</t>
+          <t>326077</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>689108</t>
+          <t>685892</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>741325</t>
+          <t>741031</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,24%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26663</t>
+          <t>25682</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54150</t>
+          <t>53018</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22256</t>
+          <t>24103</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55908</t>
+          <t>55920</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53210</t>
+          <t>51287</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98945</t>
+          <t>99407</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>203459</t>
+          <t>204591</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>230946</t>
+          <t>231927</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>364692</t>
+          <t>364680</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>398344</t>
+          <t>396497</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>579264</t>
+          <t>578802</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>624999</t>
+          <t>626922</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,44%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>471</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18918</t>
+          <t>17624</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15315</t>
+          <t>14511</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40168</t>
+          <t>37727</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18611</t>
+          <t>17728</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49793</t>
+          <t>44240</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>217355</t>
+          <t>218649</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236034</t>
+          <t>235802</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>386620</t>
+          <t>389061</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>411473</t>
+          <t>412277</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>613268</t>
+          <t>618821</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>644450</t>
+          <t>645333</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>217373</t>
+          <t>218459</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>293236</t>
+          <t>292100</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>185648</t>
+          <t>190364</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>250084</t>
+          <t>254159</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>428284</t>
+          <t>426618</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>523453</t>
+          <t>522568</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1278463</t>
+          <t>1279599</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1354326</t>
+          <t>1353240</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1448420</t>
+          <t>1444345</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1512856</t>
+          <t>1508140</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2746749</t>
+          <t>2747634</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2841918</t>
+          <t>2843584</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,95%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P59A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P59A-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21448</t>
+          <t>21499</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42861</t>
+          <t>42441</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13539</t>
+          <t>13513</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31081</t>
+          <t>30821</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39649</t>
+          <t>38560</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65914</t>
+          <t>65615</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>102450</t>
+          <t>102870</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>123863</t>
+          <t>123812</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93019</t>
+          <t>93279</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>110561</t>
+          <t>110587</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>203497</t>
+          <t>203796</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>229762</t>
+          <t>230851</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,69%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12573</t>
+          <t>12408</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27495</t>
+          <t>28297</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27654</t>
+          <t>29386</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51261</t>
+          <t>50795</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44695</t>
+          <t>45243</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72413</t>
+          <t>72201</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>95239</t>
+          <t>94437</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>110161</t>
+          <t>110326</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>113107</t>
+          <t>113573</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>136714</t>
+          <t>134982</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>214689</t>
+          <t>214901</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>242407</t>
+          <t>241859</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,24%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23732</t>
+          <t>23210</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44916</t>
+          <t>45475</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>949</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8040</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26296</t>
+          <t>25957</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48930</t>
+          <t>49795</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>114254</t>
+          <t>113695</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>135438</t>
+          <t>135960</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37264</t>
+          <t>37043</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44376</t>
+          <t>44355</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>155544</t>
+          <t>154679</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>178178</t>
+          <t>178517</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,31%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51689</t>
+          <t>51983</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82478</t>
+          <t>80709</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26565</t>
+          <t>26199</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49560</t>
+          <t>49393</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84272</t>
+          <t>84436</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>124965</t>
+          <t>121132</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>16,85%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>327358</t>
+          <t>329127</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>358147</t>
+          <t>357853</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>259527</t>
+          <t>259694</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>282522</t>
+          <t>282888</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>593958</t>
+          <t>597791</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>634651</t>
+          <t>634487</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,26%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15034</t>
+          <t>14225</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34287</t>
+          <t>34798</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17432</t>
+          <t>18258</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37639</t>
+          <t>38977</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37776</t>
+          <t>36719</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64986</t>
+          <t>64504</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>127223</t>
+          <t>126712</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>146476</t>
+          <t>147285</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>159318</t>
+          <t>157980</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>179525</t>
+          <t>178699</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>293481</t>
+          <t>293963</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>320691</t>
+          <t>321748</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,76%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>4313</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9655</t>
+          <t>9089</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26466</t>
+          <t>25329</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10353</t>
+          <t>9954</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27173</t>
+          <t>26333</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>282315</t>
+          <t>282863</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>514908</t>
+          <t>516045</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>531719</t>
+          <t>532285</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>801377</t>
+          <t>802217</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>818197</t>
+          <t>818596</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>148176</t>
+          <t>151364</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>199818</t>
+          <t>201099</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>119396</t>
+          <t>119674</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>164758</t>
+          <t>167116</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>280883</t>
+          <t>283211</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>352983</t>
+          <t>351607</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,18%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1085919</t>
+          <t>1084638</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1137561</t>
+          <t>1134373</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1216432</t>
+          <t>1214074</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1261794</t>
+          <t>1261516</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2313944</t>
+          <t>2315320</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2386044</t>
+          <t>2383716</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,38%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24420</t>
+          <t>26103</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47345</t>
+          <t>48091</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18778</t>
+          <t>18855</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39296</t>
+          <t>39633</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49728</t>
+          <t>48712</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78999</t>
+          <t>80659</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>30,07%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>105390</t>
+          <t>104644</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>128315</t>
+          <t>126632</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>76216</t>
+          <t>75879</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>96734</t>
+          <t>96657</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>189248</t>
+          <t>187588</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>218519</t>
+          <t>219535</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,84%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13564</t>
+          <t>12934</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32602</t>
+          <t>32326</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17759</t>
+          <t>18040</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35894</t>
+          <t>36906</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34478</t>
+          <t>35413</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61539</t>
+          <t>62557</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,83%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>101628</t>
+          <t>101904</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>120666</t>
+          <t>121296</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>81767</t>
+          <t>80755</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>99902</t>
+          <t>99621</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>190352</t>
+          <t>189334</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>217413</t>
+          <t>216478</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>85,94%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33336</t>
+          <t>33178</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57741</t>
+          <t>58671</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11718</t>
+          <t>11897</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27330</t>
+          <t>28478</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48392</t>
+          <t>50049</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77335</t>
+          <t>79194</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>27,06%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>136375</t>
+          <t>135445</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160780</t>
+          <t>160938</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71166</t>
+          <t>70018</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86778</t>
+          <t>86599</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>215277</t>
+          <t>213418</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>244220</t>
+          <t>242563</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>82,9%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61116</t>
+          <t>61709</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95024</t>
+          <t>94646</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57803</t>
+          <t>55432</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>87379</t>
+          <t>87398</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>128721</t>
+          <t>125450</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>175893</t>
+          <t>170855</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>322079</t>
+          <t>322457</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>355987</t>
+          <t>355394</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>235393</t>
+          <t>235374</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>264969</t>
+          <t>267340</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>563983</t>
+          <t>569021</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>611155</t>
+          <t>614426</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>83,04%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23546</t>
+          <t>22685</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45784</t>
+          <t>44484</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27816</t>
+          <t>27242</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52154</t>
+          <t>53176</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>56569</t>
+          <t>57036</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90813</t>
+          <t>87935</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,39%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>177545</t>
+          <t>178845</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>199783</t>
+          <t>200644</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>230300</t>
+          <t>229278</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>254638</t>
+          <t>255212</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>414969</t>
+          <t>417847</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>449213</t>
+          <t>448746</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,72%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>12043</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29886</t>
+          <t>30309</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12070</t>
+          <t>12121</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30725</t>
+          <t>30936</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>456031</t>
+          <t>455608</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>473632</t>
+          <t>473874</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>712151</t>
+          <t>711940</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>730806</t>
+          <t>730755</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>185926</t>
+          <t>186708</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>243598</t>
+          <t>244441</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>174627</t>
+          <t>174989</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>231653</t>
+          <t>230853</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>376100</t>
+          <t>373541</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>455811</t>
+          <t>453448</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1134873</t>
+          <t>1134030</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1192545</t>
+          <t>1191763</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1191160</t>
+          <t>1191960</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1248186</t>
+          <t>1247824</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2345473</t>
+          <t>2347836</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2425184</t>
+          <t>2427743</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,67%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16988</t>
+          <t>17124</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37326</t>
+          <t>36979</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17861</t>
+          <t>18011</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37679</t>
+          <t>38628</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39640</t>
+          <t>39684</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68038</t>
+          <t>67944</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>149648</t>
+          <t>149995</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>169986</t>
+          <t>169850</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>117007</t>
+          <t>116058</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136825</t>
+          <t>136675</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>273622</t>
+          <t>273716</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>302020</t>
+          <t>301976</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,39%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34651</t>
+          <t>34332</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57257</t>
+          <t>56863</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19048</t>
+          <t>18764</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39159</t>
+          <t>39827</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57243</t>
+          <t>58597</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86143</t>
+          <t>87484</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>31,05%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71450</t>
+          <t>71844</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>94056</t>
+          <t>94375</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>113874</t>
+          <t>113206</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>133985</t>
+          <t>134269</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>195597</t>
+          <t>194256</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>224497</t>
+          <t>223143</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,2%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20683</t>
+          <t>20731</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41578</t>
+          <t>40764</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6538</t>
+          <t>6134</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19908</t>
+          <t>19678</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31202</t>
+          <t>30523</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55500</t>
+          <t>54333</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>114051</t>
+          <t>114865</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>134946</t>
+          <t>134898</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48353</t>
+          <t>48583</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61723</t>
+          <t>62127</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>168390</t>
+          <t>169557</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>192688</t>
+          <t>193367</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,37%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78737</t>
+          <t>76964</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>112629</t>
+          <t>113037</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67581</t>
+          <t>66474</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>100110</t>
+          <t>100320</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>155197</t>
+          <t>157026</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>202344</t>
+          <t>200710</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>300172</t>
+          <t>299764</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>334064</t>
+          <t>335837</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>315945</t>
+          <t>315735</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>348474</t>
+          <t>349581</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>626512</t>
+          <t>628146</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>673659</t>
+          <t>671830</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,06%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39016</t>
+          <t>40109</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66437</t>
+          <t>68147</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38145</t>
+          <t>37562</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64785</t>
+          <t>63393</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83741</t>
+          <t>82558</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121954</t>
+          <t>121816</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>228259</t>
+          <t>226549</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>255680</t>
+          <t>254587</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>251797</t>
+          <t>253189</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>278437</t>
+          <t>279020</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>489324</t>
+          <t>489462</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>527537</t>
+          <t>528720</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,49%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13876</t>
+          <t>14525</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17649</t>
+          <t>17110</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38091</t>
+          <t>37198</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23302</t>
+          <t>23750</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45867</t>
+          <t>47112</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>263610</t>
+          <t>262961</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>274581</t>
+          <t>274576</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>441014</t>
+          <t>441907</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>461456</t>
+          <t>461995</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>710725</t>
+          <t>709480</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>733290</t>
+          <t>732842</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,86%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>225352</t>
+          <t>228063</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>287259</t>
+          <t>285689</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>197549</t>
+          <t>197404</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>254781</t>
+          <t>251335</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>439060</t>
+          <t>442040</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>519329</t>
+          <t>524427</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,23%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1169034</t>
+          <t>1170604</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1230941</t>
+          <t>1228230</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1332941</t>
+          <t>1336387</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1390173</t>
+          <t>1390318</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2524686</t>
+          <t>2519588</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2604955</t>
+          <t>2601975</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,48%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>45408</t>
+          <t>47020</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34082</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59521</t>
+          <t>61612</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>43914</t>
+          <t>46763</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34535</t>
+          <t>37364</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55638</t>
+          <t>59330</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>89322</t>
+          <t>93783</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74753</t>
+          <t>78058</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106715</t>
+          <t>111209</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>24,85%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>155833</t>
+          <t>167481</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>141720</t>
+          <t>152889</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>167170</t>
+          <t>180419</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>169954</t>
+          <t>186212</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>158230</t>
+          <t>173645</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>179333</t>
+          <t>195611</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>325787</t>
+          <t>353692</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>308394</t>
+          <t>336266</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>340356</t>
+          <t>369417</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,56%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>201241</t>
+          <t>214501</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>201241</t>
+          <t>214501</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>201241</t>
+          <t>214501</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>213868</t>
+          <t>232975</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>213868</t>
+          <t>232975</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>213868</t>
+          <t>232975</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>415109</t>
+          <t>447475</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>415109</t>
+          <t>447475</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>415109</t>
+          <t>447475</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27553</t>
+          <t>32380</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17201</t>
+          <t>21864</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41549</t>
+          <t>46809</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38061</t>
+          <t>41057</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29195</t>
+          <t>31577</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49992</t>
+          <t>53086</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>65614</t>
+          <t>73438</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51254</t>
+          <t>58014</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80280</t>
+          <t>91396</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>22,81%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>167181</t>
+          <t>172850</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>153185</t>
+          <t>158421</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>177533</t>
+          <t>183366</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>142462</t>
+          <t>154361</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>130531</t>
+          <t>142332</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>151328</t>
+          <t>163841</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>309644</t>
+          <t>327211</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>294978</t>
+          <t>309253</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>324004</t>
+          <t>342635</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>85,52%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>194734</t>
+          <t>205230</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>194734</t>
+          <t>205230</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>194734</t>
+          <t>205230</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>180523</t>
+          <t>195418</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>180523</t>
+          <t>195418</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>180523</t>
+          <t>195418</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>375258</t>
+          <t>400649</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>375258</t>
+          <t>400649</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>375258</t>
+          <t>400649</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>42630</t>
+          <t>45649</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31166</t>
+          <t>32467</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58317</t>
+          <t>61457</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8949</t>
+          <t>10561</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4942</t>
+          <t>5924</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14924</t>
+          <t>17055</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>51579</t>
+          <t>56209</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38292</t>
+          <t>42644</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68465</t>
+          <t>75411</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,41%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>139500</t>
+          <t>153476</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>123813</t>
+          <t>137668</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>150964</t>
+          <t>166658</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>67869</t>
+          <t>75898</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61894</t>
+          <t>69404</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71876</t>
+          <t>80535</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>207369</t>
+          <t>229375</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>190483</t>
+          <t>210173</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>220656</t>
+          <t>242940</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,07%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>182130</t>
+          <t>199125</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>182130</t>
+          <t>199125</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>182130</t>
+          <t>199125</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>76818</t>
+          <t>86459</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>76818</t>
+          <t>86459</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>76818</t>
+          <t>86459</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>258948</t>
+          <t>285584</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>258948</t>
+          <t>285584</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>258948</t>
+          <t>285584</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>96118</t>
+          <t>106873</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76236</t>
+          <t>84989</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>121044</t>
+          <t>131930</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>66993</t>
+          <t>78547</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53829</t>
+          <t>63911</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82232</t>
+          <t>97552</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>163111</t>
+          <t>185420</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>138588</t>
+          <t>159818</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>193727</t>
+          <t>213583</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>403594</t>
+          <t>427698</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>378668</t>
+          <t>402641</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>423476</t>
+          <t>449582</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>312913</t>
+          <t>345878</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>297674</t>
+          <t>326873</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>326077</t>
+          <t>360514</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>716508</t>
+          <t>773576</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>685892</t>
+          <t>745413</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>741031</t>
+          <t>799178</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>83,33%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>499712</t>
+          <t>534571</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>499712</t>
+          <t>534571</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>499712</t>
+          <t>534571</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>379906</t>
+          <t>424425</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>379906</t>
+          <t>424425</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>379906</t>
+          <t>424425</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>879619</t>
+          <t>958996</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>879619</t>
+          <t>958996</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>879619</t>
+          <t>958996</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>37352</t>
+          <t>40483</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25682</t>
+          <t>27479</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53018</t>
+          <t>58616</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>40546</t>
+          <t>46770</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24103</t>
+          <t>35344</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55920</t>
+          <t>58578</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>77898</t>
+          <t>87253</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51287</t>
+          <t>71433</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>99407</t>
+          <t>109255</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>220257</t>
+          <t>262645</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>204591</t>
+          <t>244512</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>231927</t>
+          <t>275649</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>380054</t>
+          <t>348783</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>364680</t>
+          <t>336975</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>396497</t>
+          <t>360209</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>600311</t>
+          <t>611428</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>578802</t>
+          <t>589426</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>626922</t>
+          <t>627248</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>89,78%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>257609</t>
+          <t>303128</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>257609</t>
+          <t>303128</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>257609</t>
+          <t>303128</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>420600</t>
+          <t>395553</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>420600</t>
+          <t>395553</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>420600</t>
+          <t>395553</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>678209</t>
+          <t>698681</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>678209</t>
+          <t>698681</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>678209</t>
+          <t>698681</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>6464</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17624</t>
+          <t>19109</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24075</t>
+          <t>25181</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14511</t>
+          <t>15785</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37727</t>
+          <t>38364</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>29145</t>
+          <t>31645</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17728</t>
+          <t>18794</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44240</t>
+          <t>48938</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>231203</t>
+          <t>226501</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>218649</t>
+          <t>213856</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>235802</t>
+          <t>231251</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>402713</t>
+          <t>447355</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>389061</t>
+          <t>434172</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>412277</t>
+          <t>456751</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>633916</t>
+          <t>673856</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>618821</t>
+          <t>656563</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>645333</t>
+          <t>686707</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>236273</t>
+          <t>232965</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>236273</t>
+          <t>232965</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>236273</t>
+          <t>232965</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>426788</t>
+          <t>472536</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>426788</t>
+          <t>472536</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>426788</t>
+          <t>472536</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>663061</t>
+          <t>705501</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>663061</t>
+          <t>705501</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>663061</t>
+          <t>705501</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>254131</t>
+          <t>278869</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>218459</t>
+          <t>241942</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>292100</t>
+          <t>320134</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>222539</t>
+          <t>248879</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>190364</t>
+          <t>220115</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>254159</t>
+          <t>277465</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>476669</t>
+          <t>527748</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>426618</t>
+          <t>479357</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>522568</t>
+          <t>575084</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1317568</t>
+          <t>1410651</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1279599</t>
+          <t>1369386</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1353240</t>
+          <t>1447578</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1475965</t>
+          <t>1558487</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1444345</t>
+          <t>1529901</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1508140</t>
+          <t>1587251</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2793533</t>
+          <t>2969138</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2747634</t>
+          <t>2921802</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2843584</t>
+          <t>3017529</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,29%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1571699</t>
+          <t>1689520</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1571699</t>
+          <t>1689520</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1571699</t>
+          <t>1689520</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1698504</t>
+          <t>1807366</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1698504</t>
+          <t>1807366</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1698504</t>
+          <t>1807366</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>3270202</t>
+          <t>3496886</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3270202</t>
+          <t>3496886</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3270202</t>
+          <t>3496886</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
